--- a/DATA/MASTER/C10_MASTER/Calidad_Variables_Dataset_Maestro_Framework_v04.xlsx
+++ b/DATA/MASTER/C10_MASTER/Calidad_Variables_Dataset_Maestro_Framework_v04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:L53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -530,7 +530,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Lista para modelado</t>
+          <t>Sin tratamiento por faltantes</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Lista para modelado</t>
+          <t>Sin tratamiento por faltantes</t>
         </is>
       </c>
     </row>
@@ -620,7 +620,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Lista para modelado</t>
+          <t>Sin tratamiento por faltantes</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Lista para modelado</t>
+          <t>Sin tratamiento por faltantes</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Lista para modelado</t>
+          <t>Sin tratamiento por faltantes</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Lista para modelado</t>
+          <t>Sin tratamiento por faltantes</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Lista para modelado</t>
+          <t>Sin tratamiento por faltantes</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Lista para modelado</t>
+          <t>Sin tratamiento por faltantes</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Lista para modelado</t>
+          <t>Sin tratamiento por faltantes</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Lista para modelado</t>
+          <t>Sin tratamiento por faltantes</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Lista para modelado</t>
+          <t>Sin tratamiento por faltantes</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Lista para modelado</t>
+          <t>Sin tratamiento por faltantes</t>
         </is>
       </c>
     </row>
@@ -1078,19 +1078,19 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Lista para modelado</t>
+          <t>Sin tratamiento por faltantes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VolumenUtilDiarioMasa</t>
+          <t>irca</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1109,13 +1109,13 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="I15" t="n">
-        <v>526</v>
+        <v>499</v>
       </c>
       <c r="J15" t="n">
-        <v>91.67</v>
+        <v>9.09</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1124,19 +1124,19 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Lista para modelado</t>
+          <t>Sin tratamiento por faltantes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>irca</t>
+          <t>nivel_de_riesgo</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1160,9 +1160,7 @@
       <c r="I16" t="n">
         <v>526</v>
       </c>
-      <c r="J16" t="n">
-        <v>90.91</v>
-      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>A - Excelente</t>
@@ -1170,19 +1168,19 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Lista para modelado</t>
+          <t>Sin tratamiento por faltantes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>nivel_de_riesgo</t>
+          <t>POBLACION TOTAL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1201,12 +1199,14 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="I17" t="n">
-        <v>526</v>
-      </c>
-      <c r="J17" t="inlineStr"/>
+        <v>512</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>A - Excelente</t>
@@ -1214,19 +1214,19 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Lista para modelado</t>
+          <t>Sin tratamiento por faltantes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>POBLACION TOTAL</t>
+          <t>ACCESO A AGUA POTABLE ADECUADO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1245,13 +1245,13 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I18" t="n">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="J18" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Lista para modelado</t>
+          <t>Sin tratamiento por faltantes</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1291,13 +1291,13 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="I19" t="n">
-        <v>526</v>
+        <v>512</v>
       </c>
       <c r="J19" t="n">
-        <v>36.36</v>
+        <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1306,19 +1306,19 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Lista para modelado</t>
+          <t>Sin tratamiento por faltantes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ACCESO A AGUA POTABLE ADECUADO</t>
+          <t>COBERTURA DE ACUEDUCTO URBANO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1343,7 +1343,7 @@
         <v>526</v>
       </c>
       <c r="J20" t="n">
-        <v>36.36</v>
+        <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Lista para modelado</t>
+          <t>Sin tratamiento por faltantes</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1383,13 +1383,13 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I21" t="n">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="J21" t="n">
-        <v>36.36</v>
+        <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1398,19 +1398,19 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Lista para modelado</t>
+          <t>Sin tratamiento por faltantes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>COBERTURA DE ACUEDUCTO URBANO</t>
+          <t>Volumen_Fuente</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1429,14 +1429,12 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I22" t="n">
-        <v>526</v>
-      </c>
-      <c r="J22" t="n">
-        <v>36.36</v>
-      </c>
+        <v>525</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>A - Excelente</t>
@@ -1444,14 +1442,14 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Lista para modelado</t>
+          <t>Sin tratamiento por faltantes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>COBERTURA DE ACUEDUCTO RURAL</t>
+          <t>AlcantarilladoUrbano_Imputado</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1490,19 +1488,19 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Lista para modelado</t>
+          <t>Sin tratamiento por faltantes</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>COBERTURA DE ALCANTARILLADO RURAL</t>
+          <t>COBERTURA DE ACUEDUCTO RURAL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1521,13 +1519,13 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I24" t="n">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="J24" t="n">
-        <v>36.36</v>
+        <v>0</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1536,7 +1534,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Lista para modelado</t>
+          <t>Sin tratamiento por faltantes</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1546,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1567,13 +1565,13 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I25" t="n">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="J25" t="n">
-        <v>36.36</v>
+        <v>0</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1582,19 +1580,19 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Lista para modelado</t>
+          <t>Sin tratamiento por faltantes</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Version_Dataset</t>
+          <t>COBERTURA DE ALCANTARILLADO RURAL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>float64</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1613,12 +1611,14 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I26" t="n">
-        <v>527</v>
-      </c>
-      <c r="J26" t="inlineStr"/>
+        <v>521</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>A - Excelente</t>
@@ -1626,14 +1626,14 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Lista para modelado</t>
+          <t>Sin tratamiento por faltantes</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Volumen_Fuente</t>
+          <t>IRCA_Fuente</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I27" t="n">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
@@ -1670,14 +1670,14 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Lista para modelado</t>
+          <t>Sin tratamiento por faltantes</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IRCA_Fuente</t>
+          <t>Version_Dataset</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1714,428 +1714,428 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Lista para modelado</t>
+          <t>Sin tratamiento por faltantes</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CONTINUIDAD DE ACUEDUCTO URBANO</t>
+          <t>AlcantarilladoRural_Imputado</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>528</v>
       </c>
       <c r="D29" t="n">
-        <v>96</v>
+        <v>528</v>
       </c>
       <c r="E29" t="n">
-        <v>432</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>18.18</v>
+        <v>100</v>
       </c>
       <c r="G29" t="n">
-        <v>81.81999999999999</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29" t="n">
-        <v>95</v>
+        <v>526</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>36.36</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>D - Baja</t>
+          <t>A - Excelente</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>No recomendable para entrenamiento</t>
+          <t>Sin tratamiento por faltantes</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AGUAS RESIDUALES TRATADAS</t>
+          <t>Saneamiento_Imputado</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>528</v>
       </c>
       <c r="D30" t="n">
-        <v>96</v>
+        <v>528</v>
       </c>
       <c r="E30" t="n">
-        <v>432</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>18.18</v>
+        <v>100</v>
       </c>
       <c r="G30" t="n">
-        <v>81.81999999999999</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I30" t="n">
-        <v>92</v>
+        <v>526</v>
       </c>
       <c r="J30" t="n">
-        <v>4.55</v>
+        <v>36.36</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>D - Baja</t>
+          <t>A - Excelente</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>No recomendable para entrenamiento</t>
+          <t>Sin tratamiento por faltantes</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CALIDAD DEL AGUA</t>
+          <t>AcueductoUrbano_Imputado</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>528</v>
       </c>
       <c r="D31" t="n">
-        <v>96</v>
+        <v>528</v>
       </c>
       <c r="E31" t="n">
-        <v>432</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>18.18</v>
+        <v>100</v>
       </c>
       <c r="G31" t="n">
-        <v>81.81999999999999</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
-        <v>88</v>
+        <v>526</v>
       </c>
       <c r="J31" t="n">
-        <v>2.27</v>
+        <v>36.36</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>D - Baja</t>
+          <t>A - Excelente</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>No recomendable para entrenamiento</t>
+          <t>Sin tratamiento por faltantes</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Nivel_Minimo</t>
+          <t>AcueductoRural_Imputado</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>528</v>
       </c>
       <c r="D32" t="n">
-        <v>87</v>
+        <v>528</v>
       </c>
       <c r="E32" t="n">
-        <v>441</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>16.48</v>
+        <v>100</v>
       </c>
       <c r="G32" t="n">
-        <v>83.52</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>83</v>
+        <v>2</v>
       </c>
       <c r="I32" t="n">
-        <v>4</v>
+        <v>526</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>36.36</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>D - Baja</t>
+          <t>A - Excelente</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>No recomendable para entrenamiento</t>
+          <t>Sin tratamiento por faltantes</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SOLIDOS SUSPENDIDOS TOTALES</t>
+          <t>AguaPotable_Imputada</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>528</v>
       </c>
       <c r="D33" t="n">
-        <v>50</v>
+        <v>528</v>
       </c>
       <c r="E33" t="n">
-        <v>478</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>9.470000000000001</v>
+        <v>100</v>
       </c>
       <c r="G33" t="n">
-        <v>90.53</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="I33" t="n">
-        <v>5</v>
+        <v>526</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>36.36</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>D - Baja</t>
+          <t>A - Excelente</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>No recomendable para entrenamiento</t>
+          <t>Sin tratamiento por faltantes</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>OXIGENO DISUELTO (OD)</t>
+          <t>Volumen_Imputado</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>528</v>
       </c>
       <c r="D34" t="n">
-        <v>50</v>
+        <v>528</v>
       </c>
       <c r="E34" t="n">
-        <v>478</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>9.470000000000001</v>
+        <v>100</v>
       </c>
       <c r="G34" t="n">
-        <v>90.53</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="I34" t="n">
-        <v>4</v>
+        <v>526</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>91.67</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>D - Baja</t>
+          <t>A - Excelente</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>No recomendable para entrenamiento</t>
+          <t>Sin tratamiento por faltantes</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CONDUCTIVIDAD ELECTRICA</t>
+          <t>Poblacion_Imputada</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>528</v>
       </c>
       <c r="D35" t="n">
-        <v>50</v>
+        <v>528</v>
       </c>
       <c r="E35" t="n">
-        <v>478</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>9.470000000000001</v>
+        <v>100</v>
       </c>
       <c r="G35" t="n">
-        <v>90.53</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>526</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>36.36</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>D - Baja</t>
+          <t>A - Excelente</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>No recomendable para entrenamiento</t>
+          <t>Sin tratamiento por faltantes</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>pH</t>
+          <t>Densidad_Imputada</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>528</v>
       </c>
       <c r="D36" t="n">
-        <v>50</v>
+        <v>528</v>
       </c>
       <c r="E36" t="n">
-        <v>478</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>9.470000000000001</v>
+        <v>100</v>
       </c>
       <c r="G36" t="n">
-        <v>90.53</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="I36" t="n">
-        <v>5</v>
+        <v>526</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>36.36</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>D - Baja</t>
+          <t>A - Excelente</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>No recomendable para entrenamiento</t>
+          <t>Sin tratamiento por faltantes</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TEMPERATURA</t>
+          <t>IRCA_Imputado</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>int64</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>528</v>
       </c>
       <c r="D37" t="n">
-        <v>50</v>
+        <v>528</v>
       </c>
       <c r="E37" t="n">
-        <v>478</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>9.470000000000001</v>
+        <v>100</v>
       </c>
       <c r="G37" t="n">
-        <v>90.53</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="I37" t="n">
-        <v>6</v>
+        <v>526</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>90.91</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>D - Baja</t>
+          <t>A - Excelente</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>No recomendable para entrenamiento</t>
+          <t>Sin tratamiento por faltantes</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FOSFORO TOTAL</t>
+          <t>VolumenUtilDiarioMasa</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2147,41 +2147,41 @@
         <v>528</v>
       </c>
       <c r="D38" t="n">
-        <v>49</v>
+        <v>336</v>
       </c>
       <c r="E38" t="n">
-        <v>479</v>
+        <v>192</v>
       </c>
       <c r="F38" t="n">
-        <v>9.279999999999999</v>
+        <v>63.64</v>
       </c>
       <c r="G38" t="n">
-        <v>90.72</v>
+        <v>36.36</v>
       </c>
       <c r="H38" t="n">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="I38" t="n">
-        <v>4</v>
+        <v>252</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>D - Baja</t>
+          <t>C - Media</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>No recomendable para entrenamiento</t>
+          <t>Requiere estrategia para datos faltantes</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
+          <t>AGUAS RESIDUALES TRATADAS</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2193,25 +2193,25 @@
         <v>528</v>
       </c>
       <c r="D39" t="n">
-        <v>49</v>
+        <v>96</v>
       </c>
       <c r="E39" t="n">
-        <v>479</v>
+        <v>432</v>
       </c>
       <c r="F39" t="n">
-        <v>9.279999999999999</v>
+        <v>18.18</v>
       </c>
       <c r="G39" t="n">
-        <v>90.72</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H39" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="I39" t="n">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2220,14 +2220,14 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>No recomendable para entrenamiento</t>
+          <t>Cobertura insuficiente; revisar uso</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>INDICE DE DESEMPENO INSTITUCIONAL</t>
+          <t>CONTINUIDAD DE ACUEDUCTO URBANO</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2239,22 +2239,22 @@
         <v>528</v>
       </c>
       <c r="D40" t="n">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="E40" t="n">
-        <v>480</v>
+        <v>432</v>
       </c>
       <c r="F40" t="n">
-        <v>9.09</v>
+        <v>18.18</v>
       </c>
       <c r="G40" t="n">
-        <v>90.91</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2266,14 +2266,14 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>No recomendable para entrenamiento</t>
+          <t>Cobertura insuficiente; revisar uso</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TURBIDEZ</t>
+          <t>CALIDAD DEL AGUA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2285,25 +2285,25 @@
         <v>528</v>
       </c>
       <c r="D41" t="n">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="E41" t="n">
-        <v>494</v>
+        <v>432</v>
       </c>
       <c r="F41" t="n">
-        <v>6.44</v>
+        <v>18.18</v>
       </c>
       <c r="G41" t="n">
-        <v>93.56</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H41" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="I41" t="n">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -2312,14 +2312,14 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>No recomendable para entrenamiento</t>
+          <t>Cobertura insuficiente; revisar uso</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NITROGENO TOTAL</t>
+          <t>Nivel_Minimo</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2331,22 +2331,22 @@
         <v>528</v>
       </c>
       <c r="D42" t="n">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="E42" t="n">
-        <v>499</v>
+        <v>441</v>
       </c>
       <c r="F42" t="n">
-        <v>5.49</v>
+        <v>16.48</v>
       </c>
       <c r="G42" t="n">
-        <v>94.51000000000001</v>
+        <v>83.52</v>
       </c>
       <c r="H42" t="n">
-        <v>29</v>
+        <v>83</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2358,53 +2358,513 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>No recomendable para entrenamiento</t>
+          <t>Cobertura insuficiente; revisar uso</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>SOLIDOS SUSPENDIDOS TOTALES</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>528</v>
+      </c>
+      <c r="D43" t="n">
+        <v>50</v>
+      </c>
+      <c r="E43" t="n">
+        <v>478</v>
+      </c>
+      <c r="F43" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="G43" t="n">
+        <v>90.53</v>
+      </c>
+      <c r="H43" t="n">
+        <v>45</v>
+      </c>
+      <c r="I43" t="n">
+        <v>5</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>D - Baja</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Cobertura insuficiente; revisar uso</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>CONDUCTIVIDAD ELECTRICA</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>528</v>
+      </c>
+      <c r="D44" t="n">
+        <v>50</v>
+      </c>
+      <c r="E44" t="n">
+        <v>478</v>
+      </c>
+      <c r="F44" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="G44" t="n">
+        <v>90.53</v>
+      </c>
+      <c r="H44" t="n">
+        <v>50</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>D - Baja</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Cobertura insuficiente; revisar uso</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>OXIGENO DISUELTO (OD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>528</v>
+      </c>
+      <c r="D45" t="n">
+        <v>50</v>
+      </c>
+      <c r="E45" t="n">
+        <v>478</v>
+      </c>
+      <c r="F45" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="G45" t="n">
+        <v>90.53</v>
+      </c>
+      <c r="H45" t="n">
+        <v>46</v>
+      </c>
+      <c r="I45" t="n">
+        <v>4</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>D - Baja</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Cobertura insuficiente; revisar uso</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>528</v>
+      </c>
+      <c r="D46" t="n">
+        <v>50</v>
+      </c>
+      <c r="E46" t="n">
+        <v>478</v>
+      </c>
+      <c r="F46" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="G46" t="n">
+        <v>90.53</v>
+      </c>
+      <c r="H46" t="n">
+        <v>45</v>
+      </c>
+      <c r="I46" t="n">
+        <v>5</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>D - Baja</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Cobertura insuficiente; revisar uso</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>TEMPERATURA</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>528</v>
+      </c>
+      <c r="D47" t="n">
+        <v>50</v>
+      </c>
+      <c r="E47" t="n">
+        <v>478</v>
+      </c>
+      <c r="F47" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="G47" t="n">
+        <v>90.53</v>
+      </c>
+      <c r="H47" t="n">
+        <v>44</v>
+      </c>
+      <c r="I47" t="n">
+        <v>6</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>D - Baja</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Cobertura insuficiente; revisar uso</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>528</v>
+      </c>
+      <c r="D48" t="n">
+        <v>49</v>
+      </c>
+      <c r="E48" t="n">
+        <v>479</v>
+      </c>
+      <c r="F48" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="G48" t="n">
+        <v>90.72</v>
+      </c>
+      <c r="H48" t="n">
+        <v>44</v>
+      </c>
+      <c r="I48" t="n">
+        <v>5</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>D - Baja</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Cobertura insuficiente; revisar uso</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>FOSFORO TOTAL</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>528</v>
+      </c>
+      <c r="D49" t="n">
+        <v>49</v>
+      </c>
+      <c r="E49" t="n">
+        <v>479</v>
+      </c>
+      <c r="F49" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="G49" t="n">
+        <v>90.72</v>
+      </c>
+      <c r="H49" t="n">
+        <v>45</v>
+      </c>
+      <c r="I49" t="n">
+        <v>4</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>D - Baja</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Cobertura insuficiente; revisar uso</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>INDICE DE DESEMPENO INSTITUCIONAL</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>528</v>
+      </c>
+      <c r="D50" t="n">
+        <v>48</v>
+      </c>
+      <c r="E50" t="n">
+        <v>480</v>
+      </c>
+      <c r="F50" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="G50" t="n">
+        <v>90.91</v>
+      </c>
+      <c r="H50" t="n">
+        <v>4</v>
+      </c>
+      <c r="I50" t="n">
+        <v>44</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>D - Baja</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Cobertura insuficiente; revisar uso</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>TURBIDEZ</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>528</v>
+      </c>
+      <c r="D51" t="n">
+        <v>34</v>
+      </c>
+      <c r="E51" t="n">
+        <v>494</v>
+      </c>
+      <c r="F51" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="G51" t="n">
+        <v>93.56</v>
+      </c>
+      <c r="H51" t="n">
+        <v>30</v>
+      </c>
+      <c r="I51" t="n">
+        <v>4</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>D - Baja</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Cobertura insuficiente; revisar uso</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>NITROGENO TOTAL</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>528</v>
+      </c>
+      <c r="D52" t="n">
+        <v>29</v>
+      </c>
+      <c r="E52" t="n">
+        <v>499</v>
+      </c>
+      <c r="F52" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="G52" t="n">
+        <v>94.51000000000001</v>
+      </c>
+      <c r="H52" t="n">
+        <v>29</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>D - Baja</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Cobertura insuficiente; revisar uso</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>float64</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>528</v>
-      </c>
-      <c r="D43" t="n">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>528</v>
+      </c>
+      <c r="D53" t="n">
         <v>26</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E53" t="n">
         <v>502</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F53" t="n">
         <v>4.92</v>
       </c>
-      <c r="G43" t="n">
+      <c r="G53" t="n">
         <v>95.08</v>
       </c>
-      <c r="H43" t="n">
+      <c r="H53" t="n">
         <v>19</v>
       </c>
-      <c r="I43" t="n">
+      <c r="I53" t="n">
         <v>7</v>
       </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="inlineStr">
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="inlineStr">
         <is>
           <t>D - Baja</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>No recomendable para entrenamiento</t>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Cobertura insuficiente; revisar uso</t>
         </is>
       </c>
     </row>
